--- a/ISAPP.xlsx
+++ b/ISAPP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77b182df1aa05c7f/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{2B9801D3-7FA3-4F2A-8A67-32BC86732106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85E5ED8-4954-4A80-A04E-9011EEACD38E}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{2B9801D3-7FA3-4F2A-8A67-32BC86732106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A2C6246-732F-4907-AC70-A95104B22B4D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="291" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="291" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TITULAR" sheetId="1" r:id="rId1"/>
@@ -321,10 +321,10 @@
   <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="000&quot;.&quot;000&quot;.&quot;000&quot;-&quot;00"/>
-    <numFmt numFmtId="169" formatCode="00000&quot;-&quot;000"/>
-    <numFmt numFmtId="170" formatCode="&quot;(&quot;00&quot;)&quot;0000&quot;-&quot;0000"/>
-    <numFmt numFmtId="171" formatCode="&quot;(&quot;00&quot;)&quot;00000&quot;-&quot;0000"/>
-    <numFmt numFmtId="172" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="00000&quot;-&quot;000"/>
+    <numFmt numFmtId="166" formatCode="&quot;(&quot;00&quot;)&quot;0000&quot;-&quot;0000"/>
+    <numFmt numFmtId="167" formatCode="&quot;(&quot;00&quot;)&quot;00000&quot;-&quot;0000"/>
+    <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -454,12 +454,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="172" fontId="7" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -469,9 +463,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -479,7 +470,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
@@ -491,7 +482,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -511,21 +502,30 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5362,114 +5362,114 @@
   </cols>
   <sheetData>
     <row r="6" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="16">
         <v>12345678910</v>
       </c>
     </row>
     <row r="8" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="17">
         <v>30222</v>
       </c>
     </row>
     <row r="9" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="18">
         <v>109900210225</v>
       </c>
     </row>
     <row r="10" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="15" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="19">
         <v>12344500</v>
       </c>
     </row>
     <row r="14" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="20">
         <v>2112341234</v>
       </c>
     </row>
     <row r="15" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="21">
         <v>21912341234</v>
       </c>
     </row>
     <row r="16" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="22" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="3:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" spans="3:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="15" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5505,11 +5505,11 @@
       <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="24">
         <f>SUM(E10,E16,E22)</f>
         <v>27380</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C8" s="3" t="s">
@@ -5521,7 +5521,7 @@
       <c r="D9" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="10" t="s">
         <v>69</v>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
       <c r="D10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="11">
         <v>10000</v>
       </c>
     </row>
@@ -5539,28 +5539,28 @@
       <c r="D11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="10" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E12" s="8"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E13" s="8"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C15" s="2"/>
       <c r="D15" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="10" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       <c r="D16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="11">
         <v>4600</v>
       </c>
     </row>
@@ -5578,28 +5578,28 @@
       <c r="D17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="8"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="8"/>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C21" s="2"/>
       <c r="D21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="10" t="s">
         <v>33</v>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       <c r="D22" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="11">
         <v>12780</v>
       </c>
     </row>
@@ -5617,11 +5617,12 @@
       <c r="D23" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="10" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="x7Piaa84Imdp0uD83u3YvnxYLKz7HnWWJNxXNOgACahb8RfVvgaajpbBe9jhWCOhMEplPjpqBu041eCn5rYx5g==" saltValue="YhIKDZfBRIzTTiY4WVO1ag==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="D6:E6"/>
   </mergeCells>
@@ -5653,117 +5654,118 @@
   </cols>
   <sheetData>
     <row r="6" spans="3:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
     </row>
     <row r="7" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="9" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="15">
+      <c r="C8" s="12">
         <v>45775</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="14">
         <v>3000</v>
       </c>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="15">
+      <c r="C9" s="12">
         <v>45787</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="14">
         <v>7530</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="15">
+      <c r="C10" s="12">
         <v>45792</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="14">
         <v>3500</v>
       </c>
     </row>
     <row r="11" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="15"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
     </row>
     <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="15"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="+K09RGmyZjmOlRh2LZHlN4Dq5CehRt2LwEsSFbyUwrz0tSzNk8d2/Mo2Wa8qtcRI8IDIiEwVwjKspA31bZEhpw==" saltValue="KAEfCyAGtBokGjcZ8R+IhQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <autoFilter ref="C7:E7" xr:uid="{CED0A4BB-FF89-40D1-844A-4DB18C586D9C}"/>
   <mergeCells count="1">
     <mergeCell ref="C6:E6"/>
